--- a/templates/03-yeu-cau-theo-cap-do/checklist-tu-danh-gia-cap-1-5.xlsx
+++ b/templates/03-yeu-cau-theo-cap-do/checklist-tu-danh-gia-cap-1-5.xlsx
@@ -16,9 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cấp 5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cấp 1'!$A$4:$I$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cấp 1'!$A$4:$I$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cấp 1'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cấp 2'!$A$4:$I$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Cấp 2'!$A$4:$I$135</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cấp 2'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Cấp 3'!$A$4:$I$199</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cấp 3'!$4:$4</definedName>
@@ -849,23 +849,23 @@
         </is>
       </c>
       <c r="D5" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B5)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B5)</f>
         <v/>
       </c>
       <c r="E5" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B5,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B5,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B5,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B5,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G5" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B5,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B5,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H5" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B5,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B5,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I5" s="7">
@@ -894,23 +894,23 @@
         </is>
       </c>
       <c r="D6" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B6)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B6)</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B6,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B6,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B6,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B6,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G6" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B6,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B6,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H6" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B6,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B6,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I6" s="7">
@@ -939,23 +939,23 @@
         </is>
       </c>
       <c r="D7" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B7)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B7)</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B7,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B7,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B7,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B7,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B7,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B7,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H7" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B7,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B7,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I7" s="7">
@@ -984,23 +984,23 @@
         </is>
       </c>
       <c r="D8" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B8)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B8)</f>
         <v/>
       </c>
       <c r="E8" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B8,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B8,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F8" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B8,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B8,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G8" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B8,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B8,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H8" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B8,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B8,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I8" s="7">
@@ -1029,23 +1029,23 @@
         </is>
       </c>
       <c r="D9" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B9)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B9)</f>
         <v/>
       </c>
       <c r="E9" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B9,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B9,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B9,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B9,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G9" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B9,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B9,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H9" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B9,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B9,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I9" s="7">
@@ -1074,23 +1074,23 @@
         </is>
       </c>
       <c r="D10" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B10)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B10)</f>
         <v/>
       </c>
       <c r="E10" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B10,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B10,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F10" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B10,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B10,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G10" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B10,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B10,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H10" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B10,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B10,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I10" s="7">
@@ -1119,23 +1119,23 @@
         </is>
       </c>
       <c r="D11" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B11)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B11)</f>
         <v/>
       </c>
       <c r="E11" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B11,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B11,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F11" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B11,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B11,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G11" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B11,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B11,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H11" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B11,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B11,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I11" s="7">
@@ -1164,23 +1164,23 @@
         </is>
       </c>
       <c r="D12" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B12)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B12)</f>
         <v/>
       </c>
       <c r="E12" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B12,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B12,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F12" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B12,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B12,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G12" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B12,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B12,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H12" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B12,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B12,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I12" s="7">
@@ -1209,23 +1209,23 @@
         </is>
       </c>
       <c r="D13" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B13)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B13)</f>
         <v/>
       </c>
       <c r="E13" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B13,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B13,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B13,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B13,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G13" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B13,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B13,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H13" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B13,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B13,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I13" s="7">
@@ -1254,23 +1254,23 @@
         </is>
       </c>
       <c r="D14" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B14)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B14)</f>
         <v/>
       </c>
       <c r="E14" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B14,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B14,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F14" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B14,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B14,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G14" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B14,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B14,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H14" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B14,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B14,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I14" s="7">
@@ -1299,23 +1299,23 @@
         </is>
       </c>
       <c r="D15" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B15)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B15)</f>
         <v/>
       </c>
       <c r="E15" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B15,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B15,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F15" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B15,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B15,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G15" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B15,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B15,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H15" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B15,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B15,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I15" s="7">
@@ -1344,23 +1344,23 @@
         </is>
       </c>
       <c r="D16" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B16)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B16)</f>
         <v/>
       </c>
       <c r="E16" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B16,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B16,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F16" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B16,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B16,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B16,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B16,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H16" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B16,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B16,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I16" s="7">
@@ -1389,23 +1389,23 @@
         </is>
       </c>
       <c r="D17" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B17)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B17)</f>
         <v/>
       </c>
       <c r="E17" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B17,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B17,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F17" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B17,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B17,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G17" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B17,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B17,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H17" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B17,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B17,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I17" s="7">
@@ -1434,23 +1434,23 @@
         </is>
       </c>
       <c r="D18" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B18)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B18)</f>
         <v/>
       </c>
       <c r="E18" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B18,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B18,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F18" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B18,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B18,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G18" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B18,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B18,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H18" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B18,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B18,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I18" s="7">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="D19" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B19)</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B19)</f>
         <v/>
       </c>
       <c r="E19" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B19,'Cấp 1'!$E$5:$E$113,"Đạt")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B19,'Cấp 1'!$E$5:$E$115,"Đạt")</f>
         <v/>
       </c>
       <c r="F19" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B19,'Cấp 1'!$E$5:$E$113,"Một phần")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B19,'Cấp 1'!$E$5:$E$115,"Một phần")</f>
         <v/>
       </c>
       <c r="G19" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B19,'Cấp 1'!$E$5:$E$113,"Chưa")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B19,'Cấp 1'!$E$5:$E$115,"Chưa")</f>
         <v/>
       </c>
       <c r="H19" s="7">
-        <f>COUNTIFS('Cấp 1'!$A$5:$A$113,B19,'Cấp 1'!$E$5:$E$113,"N/A")</f>
+        <f>COUNTIFS('Cấp 1'!$A$5:$A$115,B19,'Cấp 1'!$E$5:$E$115,"N/A")</f>
         <v/>
       </c>
       <c r="I19" s="7">
@@ -1617,23 +1617,23 @@
         </is>
       </c>
       <c r="D23" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B23)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B23)</f>
         <v/>
       </c>
       <c r="E23" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B23,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B23,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F23" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B23,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B23,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G23" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B23,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B23,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H23" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B23,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B23,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I23" s="7">
@@ -1662,23 +1662,23 @@
         </is>
       </c>
       <c r="D24" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B24)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B24)</f>
         <v/>
       </c>
       <c r="E24" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B24,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B24,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F24" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B24,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B24,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G24" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B24,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B24,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H24" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B24,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B24,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I24" s="7">
@@ -1707,23 +1707,23 @@
         </is>
       </c>
       <c r="D25" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B25)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B25)</f>
         <v/>
       </c>
       <c r="E25" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B25,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B25,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F25" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B25,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B25,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G25" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B25,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B25,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H25" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B25,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B25,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I25" s="7">
@@ -1752,23 +1752,23 @@
         </is>
       </c>
       <c r="D26" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B26)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B26)</f>
         <v/>
       </c>
       <c r="E26" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B26,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B26,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F26" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B26,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B26,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G26" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B26,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B26,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H26" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B26,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B26,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I26" s="7">
@@ -1797,23 +1797,23 @@
         </is>
       </c>
       <c r="D27" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B27)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B27)</f>
         <v/>
       </c>
       <c r="E27" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B27,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B27,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F27" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B27,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B27,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G27" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B27,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B27,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H27" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B27,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B27,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I27" s="7">
@@ -1842,23 +1842,23 @@
         </is>
       </c>
       <c r="D28" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B28)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B28)</f>
         <v/>
       </c>
       <c r="E28" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B28,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B28,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F28" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B28,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B28,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G28" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B28,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B28,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H28" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B28,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B28,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I28" s="7">
@@ -1887,23 +1887,23 @@
         </is>
       </c>
       <c r="D29" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B29)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B29)</f>
         <v/>
       </c>
       <c r="E29" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B29,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B29,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F29" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B29,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B29,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G29" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B29,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B29,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H29" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B29,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B29,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I29" s="7">
@@ -1932,23 +1932,23 @@
         </is>
       </c>
       <c r="D30" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B30)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B30)</f>
         <v/>
       </c>
       <c r="E30" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B30,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B30,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F30" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B30,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B30,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G30" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B30,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B30,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H30" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B30,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B30,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I30" s="7">
@@ -1977,23 +1977,23 @@
         </is>
       </c>
       <c r="D31" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B31)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B31)</f>
         <v/>
       </c>
       <c r="E31" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B31,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B31,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F31" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B31,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B31,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G31" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B31,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B31,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H31" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B31,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B31,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I31" s="7">
@@ -2022,23 +2022,23 @@
         </is>
       </c>
       <c r="D32" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B32)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B32)</f>
         <v/>
       </c>
       <c r="E32" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B32,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B32,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F32" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B32,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B32,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G32" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B32,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B32,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H32" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B32,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B32,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I32" s="7">
@@ -2067,23 +2067,23 @@
         </is>
       </c>
       <c r="D33" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B33)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B33)</f>
         <v/>
       </c>
       <c r="E33" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B33,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B33,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F33" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B33,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B33,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G33" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B33,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B33,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H33" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B33,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B33,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I33" s="7">
@@ -2112,23 +2112,23 @@
         </is>
       </c>
       <c r="D34" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B34)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B34)</f>
         <v/>
       </c>
       <c r="E34" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B34,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B34,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F34" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B34,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B34,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G34" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B34,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B34,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H34" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B34,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B34,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I34" s="7">
@@ -2157,23 +2157,23 @@
         </is>
       </c>
       <c r="D35" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B35)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B35)</f>
         <v/>
       </c>
       <c r="E35" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B35,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B35,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F35" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B35,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B35,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G35" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B35,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B35,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H35" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B35,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B35,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I35" s="7">
@@ -2202,23 +2202,23 @@
         </is>
       </c>
       <c r="D36" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B36)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B36)</f>
         <v/>
       </c>
       <c r="E36" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B36,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B36,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F36" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B36,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B36,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G36" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B36,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B36,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H36" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B36,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B36,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I36" s="7">
@@ -2247,23 +2247,23 @@
         </is>
       </c>
       <c r="D37" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B37)</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B37)</f>
         <v/>
       </c>
       <c r="E37" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B37,'Cấp 2'!$E$5:$E$133,"Đạt")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B37,'Cấp 2'!$E$5:$E$135,"Đạt")</f>
         <v/>
       </c>
       <c r="F37" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B37,'Cấp 2'!$E$5:$E$133,"Một phần")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B37,'Cấp 2'!$E$5:$E$135,"Một phần")</f>
         <v/>
       </c>
       <c r="G37" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B37,'Cấp 2'!$E$5:$E$133,"Chưa")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B37,'Cấp 2'!$E$5:$E$135,"Chưa")</f>
         <v/>
       </c>
       <c r="H37" s="7">
-        <f>COUNTIFS('Cấp 2'!$A$5:$A$133,B37,'Cấp 2'!$E$5:$E$133,"N/A")</f>
+        <f>COUNTIFS('Cấp 2'!$A$5:$A$135,B37,'Cấp 2'!$E$5:$E$135,"N/A")</f>
         <v/>
       </c>
       <c r="I37" s="7">
@@ -5036,7 +5036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6090,13 +6090,13 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Quy trình, công cụ cấp/thu hồi quyền cho 4 loại tài khoản (quản trị, tác nghiệp, kỹ thuật, dịch vụ) theo vai trò</t>
+          <t>Có quy trình, công cụ phân quyền và quản lý quyền truy cập cho 4 loại tài khoản (quản trị, tác nghiệp, kỹ thuật, dịch vụ)</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr"/>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Quy trình quản lý tài khoản</t>
+          <t>Quy trình quản lý tài khoản, công cụ quản lý tập trung</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
@@ -6116,18 +6116,18 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>3.6.1 c)</t>
+          <t>3.6.1 b)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Ghi log và giám sát hoạt động của tài khoản người dùng</t>
+          <t>Quy trình tạo, gán, quản lý, thu hồi đặc quyền và quyền truy cập; quyền của từng loại tài khoản nhất quán theo vai trò, chỉ đủ cho dữ liệu, tài sản cần thiết</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình audit log đăng nhập</t>
+          <t>Quy trình cấp/thu hồi quyền, phiếu yêu cầu đã duyệt</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
@@ -6147,18 +6147,18 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.1 a)</t>
+          <t>3.6.1 c)</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Danh sách mọi tài khoản trên phần cứng và phần mềm</t>
+          <t>Ghi log và giám sát hoạt động của tài khoản người dùng</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr"/>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Danh sách tài khoản</t>
+          <t>Cấu hình audit log đăng nhập</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
@@ -6178,18 +6178,18 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.1 b)</t>
+          <t>3.6.2.1 a)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Danh sách gồm đủ loại: quản trị, tác nghiệp, dịch vụ, kỹ thuật</t>
+          <t>Danh sách mọi tài khoản trên phần cứng và phần mềm</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Danh sách tài khoản phân loại</t>
+          <t>Danh sách tài khoản</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr"/>
@@ -6209,18 +6209,18 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.1 c)</t>
+          <t>3.6.2.1 b)</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Trường tối thiểu: loại, tên, trạng thái, hệ thống, người quản lý, phòng ban, ngày kích hoạt/vô hiệu; không còn tài khoản không hợp lệ</t>
+          <t>Danh sách gồm đủ loại: quản trị, tác nghiệp, dịch vụ, kỹ thuật</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>Danh sách có đủ trường</t>
+          <t>Danh sách tài khoản phân loại</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr"/>
@@ -6240,18 +6240,18 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.1 d)</t>
+          <t>3.6.2.1 c)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Rà soát danh sách tài khoản ≥ 1 lần/năm</t>
+          <t>Trường tối thiểu: loại, tên, trạng thái, hệ thống, người quản lý, phòng ban, ngày kích hoạt/vô hiệu; không còn tài khoản không hợp lệ</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Biên bản rà soát</t>
+          <t>Danh sách có đủ trường</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
@@ -6271,18 +6271,18 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.2 a)</t>
+          <t>3.6.2.1 d)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình bắt đổi mật khẩu mặc định; quy tắc độ dài, loại ký tự</t>
+          <t>Rà soát danh sách tài khoản ≥ 1 lần/năm</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Chính sách mật khẩu (GPO/IdP)</t>
+          <t>Biên bản rà soát</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
@@ -6302,18 +6302,18 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.2 b)</t>
+          <t>3.6.2.2 a)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Gợi ý: mật khẩu riêng cho từng tài sản hoặc xác thực tập trung; bắt đổi ở lần đăng nhập đầu</t>
+          <t>Cấu hình bắt đổi mật khẩu mặc định; quy tắc độ dài, loại ký tự</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình IdP/SSO</t>
+          <t>Chính sách mật khẩu (GPO/IdP)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr"/>
@@ -6338,13 +6338,13 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Gợi ý độ dài: ≥ 8 ký tự nếu có MFA; ≥ 14 ký tự gồm đủ 4 loại ký tự nếu không có MFA</t>
+          <t>Gợi ý: mật khẩu riêng cho từng tài sản hoặc xác thực tập trung; bắt đổi ở lần đăng nhập đầu</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Chính sách mật khẩu</t>
+          <t>Cấu hình IdP/SSO</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
@@ -6369,13 +6369,13 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Tài khoản quản trị đổi mật khẩu ít nhất 2 tháng/lần</t>
+          <t>Gợi ý độ dài: ≥ 8 ký tự nếu có MFA; ≥ 14 ký tự gồm đủ 4 loại ký tự nếu không có MFA</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Chính sách hết hạn mật khẩu tài khoản quản trị</t>
+          <t>Chính sách mật khẩu</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
@@ -6395,18 +6395,18 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.3</t>
+          <t>3.6.2.2 b)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Đổi hoặc vô hiệu hóa tài khoản mặc định (root, administrator, tài khoản cài sẵn của hãng)</t>
+          <t>Tài khoản quản trị đổi mật khẩu ít nhất 2 tháng/lần</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Danh sách tài khoản mặc định đã xử lý</t>
+          <t>Chính sách hết hạn mật khẩu tài khoản quản trị</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
@@ -6431,13 +6431,13 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Tách biệt quản lý 4 loại tài khoản</t>
+          <t>Đổi hoặc vô hiệu hóa tài khoản mặc định (root, administrator, tài khoản cài sẵn của hãng)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Quy định + danh sách phân loại</t>
+          <t>Danh sách tài khoản mặc định đã xử lý</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr"/>
@@ -6462,13 +6462,13 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Mỗi tài khoản gắn một người; dùng chung phải được phê duyệt và truy vết được người dùng từng thời điểm</t>
+          <t>Tách biệt quản lý 4 loại tài khoản</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Phê duyệt tài khoản dùng chung, sổ theo dõi</t>
+          <t>Quy định + danh sách phân loại</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr"/>
@@ -6493,13 +6493,13 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Xóa/vô hiệu hóa tài khoản không hoạt động quá 45 ngày hoặc ngay khi đổi nhân sự</t>
+          <t>Mỗi tài khoản gắn một người; dùng chung phải được phê duyệt và truy vết được người dùng từng thời điểm</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo tài khoản inactive</t>
+          <t>Phê duyệt tài khoản dùng chung, sổ theo dõi</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
@@ -6524,13 +6524,13 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy định quản lý tài khoản ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Xóa/vô hiệu hóa tài khoản không hoạt động quá 45 ngày hoặc ngay khi đổi nhân sự</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Báo cáo tài khoản inactive</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
@@ -6550,18 +6550,18 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>3.6.2.4</t>
+          <t>3.6.2.3</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Áp dụng đặc quyền tối thiểu và phân tách nhiệm vụ cho mọi loại tài khoản</t>
+          <t>Rà soát quy định quản lý tài khoản ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Ma trận vai trò – quyền</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
@@ -6586,13 +6586,13 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Tài liệu hóa quyền cần thiết theo chức danh, bộ phận</t>
+          <t>Áp dụng đặc quyền tối thiểu và phân tách nhiệm vụ cho mọi loại tài khoản</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Ma trận quyền theo chức danh</t>
+          <t>Ma trận vai trò – quyền</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
@@ -6617,13 +6617,13 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>MFA cho truy cập từ ngoài tổ chức, từ đối tác/bên thứ ba, từ Internet và cho tài khoản quản trị</t>
+          <t>Tài liệu hóa quyền cần thiết theo chức danh, bộ phận</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình MFA</t>
+          <t>Ma trận quyền theo chức danh</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
@@ -6648,13 +6648,13 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy định quản lý truy cập ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>MFA cho truy cập từ ngoài tổ chức, từ đối tác/bên thứ ba, từ Internet và cho tài khoản quản trị</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Cấu hình MFA</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
@@ -6664,28 +6664,28 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Quản lý lỗ hổng bảo mật</t>
+          <t>Quản lý tài khoản và quyền truy cập</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>3.7.1 b)</t>
+          <t>3.6.2.4</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Theo dõi thông tin mối đe dọa, lỗ hổng mới từ nhiều nguồn</t>
+          <t>Rà soát quy định quản lý truy cập ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Nguồn tin đăng ký (NCSC, CVE, hãng…)</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr"/>
@@ -6705,18 +6705,18 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>3.7.2.1 a)</t>
+          <t>3.7.1 a)</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Quy trình quản lý lỗ hổng: rà quét phát hiện, chấm mức nghiêm trọng, chia sẻ/tiếp nhận báo cáo, khắc phục theo ưu tiên và kiểm tra lại</t>
+          <t>Có kế hoạch đánh giá, theo dõi lỗ hổng thường xuyên để khắc phục và giảm nguy cơ bị tấn công</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Quy trình quản lý lỗ hổng</t>
+          <t>Kế hoạch đánh giá lỗ hổng (phạm vi, lịch rà quét)</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
@@ -6736,18 +6736,18 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>3.7.2.1 b)</t>
+          <t>3.7.1 b)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy trình và thực hiện rà quét lỗ hổng ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Theo dõi thông tin mối đe dọa, lỗ hổng mới từ nhiều nguồn</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo rà quét, biên bản rà soát</t>
+          <t>Nguồn tin đăng ký (NCSC, CVE, hãng…)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
@@ -6767,18 +6767,18 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>3.7.2.2</t>
+          <t>3.7.2.1 a)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Kiểm tra, cập nhật bản vá HĐH và ứng dụng cho máy tính, di động cấp cho người dùng ≥ 1 lần/tháng</t>
+          <t>Quy trình quản lý lỗ hổng: rà quét phát hiện, chấm mức nghiêm trọng, chia sẻ/tiếp nhận báo cáo, khắc phục theo ưu tiên và kiểm tra lại</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr"/>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo tuân thủ bản vá hằng tháng</t>
+          <t>Quy trình quản lý lỗ hổng</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
@@ -6798,18 +6798,18 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>3.7.2.2</t>
+          <t>3.7.2.1 b)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Giám sát để phát hiện lỗ hổng mới và vá kịp thời</t>
+          <t>Rà soát quy trình và thực hiện rà quét lỗ hổng ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Nhật ký vá</t>
+          <t>Báo cáo rà quét, biên bản rà soát</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
@@ -6819,28 +6819,28 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhật ký an ninh mạng</t>
+          <t>Quản lý lỗ hổng bảo mật</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>3.8.2.1 a)</t>
+          <t>3.7.2.2</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Quy định quản lý log: cách ghi, thu thập, kiểm tra, lưu trữ</t>
+          <t>Kiểm tra, cập nhật bản vá HĐH và ứng dụng cho máy tính, di động cấp cho người dùng ≥ 1 lần/tháng</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Quy định quản lý nhật ký</t>
+          <t>Báo cáo tuân thủ bản vá hằng tháng</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
@@ -6850,28 +6850,28 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhật ký an ninh mạng</t>
+          <t>Quản lý lỗ hổng bảo mật</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>3.8.2.1 a)</t>
+          <t>3.7.2.2</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Thu thập tối thiểu: log truy cập phần cứng, log truy cập phần mềm, log cảnh báo của thiết bị bảo mật</t>
+          <t>Giám sát để phát hiện lỗ hổng mới và vá kịp thời</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Danh sách nguồn log</t>
+          <t>Nhật ký vá</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr"/>
@@ -6896,13 +6896,13 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Đồng bộ thời gian qua máy chủ thời gian (NTP) cho mọi thành phần tham gia giám sát</t>
+          <t>Quy định quản lý log: cách ghi, thu thập, kiểm tra, lưu trữ</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình NTP</t>
+          <t>Quy định quản lý nhật ký</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
@@ -6927,13 +6927,13 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Rà soát log ANM ≥ 1 lần/năm</t>
+          <t>Thu thập tối thiểu: log truy cập phần cứng, log truy cập phần mềm, log cảnh báo của thiết bị bảo mật</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Biên bản rà soát log</t>
+          <t>Danh sách nguồn log</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr"/>
@@ -6953,18 +6953,18 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>3.8.2.1 b)</t>
+          <t>3.8.2.1 a)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Kiểm tra, cập nhật quy trình quản lý log ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Đồng bộ thời gian qua máy chủ thời gian (NTP) cho mọi thành phần tham gia giám sát</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Cấu hình NTP</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr"/>
@@ -6974,28 +6974,28 @@
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Bảo vệ trình duyệt web, thư điện tử</t>
+          <t>Quản lý nhật ký an ninh mạng</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>3.9.2.1 a)</t>
+          <t>3.8.2.1 a)</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Danh sách trình duyệt và dịch vụ email được phép</t>
+          <t>Rà soát log ANM ≥ 1 lần/năm</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Danh sách được phép</t>
+          <t>Biên bản rà soát log</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
@@ -7005,28 +7005,28 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Bảo vệ trình duyệt web, thư điện tử</t>
+          <t>Quản lý nhật ký an ninh mạng</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>3.9.2.1 b)</t>
+          <t>3.8.2.1 b)</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Chỉ dùng phiên bản còn được hãng hỗ trợ</t>
+          <t>Kiểm tra, cập nhật quy trình quản lý log ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo phiên bản</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr"/>
@@ -7046,18 +7046,18 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>3.9.2.1 c)</t>
+          <t>3.9.2.1 a)</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật bản vá trình duyệt, email thường xuyên (hoặc biện pháp tương đương)</t>
+          <t>Danh sách trình duyệt và dịch vụ email được phép</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo bản vá</t>
+          <t>Danh sách được phép</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
@@ -7077,18 +7077,18 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>3.9.2.2</t>
+          <t>3.9.2.1 b)</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Dùng dịch vụ lọc tên miền (DNS filtering) chặn tên miền giả mạo, độc hại</t>
+          <t>Chỉ dùng phiên bản còn được hãng hỗ trợ</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình DNS filtering</t>
+          <t>Báo cáo phiên bản</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
@@ -7098,28 +7098,28 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Phòng chống phần mềm độc hại</t>
+          <t>Bảo vệ trình duyệt web, thư điện tử</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>3.10.1 a)</t>
+          <t>3.9.2.1 c)</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Quy định phòng, chống, khắc phục mã độc</t>
+          <t>Cập nhật bản vá trình duyệt, email thường xuyên (hoặc biện pháp tương đương)</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Quy định phòng chống mã độc</t>
+          <t>Báo cáo bản vá</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr"/>
@@ -7129,28 +7129,28 @@
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Phòng chống phần mềm độc hại</t>
+          <t>Bảo vệ trình duyệt web, thư điện tử</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>3.10.1 b)</t>
+          <t>3.9.2.2</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Chống mã độc cho mọi tài sản và điểm kết nối (trong và ngoài); tự quét, chặn, cập nhật mẫu, gắn với quy trình lỗ hổng/sự cố</t>
+          <t>Dùng dịch vụ lọc tên miền (DNS filtering) chặn tên miền giả mạo, độc hại</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Kiến trúc giải pháp</t>
+          <t>Cấu hình DNS filtering</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
@@ -7170,18 +7170,18 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>3.10.2.1 a)</t>
+          <t>3.10.1 a)</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Cài và duy trì phần mềm chống mã độc (hoặc tương đương) trên máy chủ, máy người dùng</t>
+          <t>Quy định phòng, chống, khắc phục mã độc</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo độ phủ agent</t>
+          <t>Quy định phòng chống mã độc</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
@@ -7201,18 +7201,18 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>3.10.2.1 b)</t>
+          <t>3.10.1 b)</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Tính năng tối thiểu: bảo vệ thời gian thực, tự cập nhật mẫu nhận diện</t>
+          <t>Chống mã độc cho mọi tài sản và điểm kết nối (trong và ngoài); tự quét, chặn, cập nhật mẫu, gắn với quy trình lỗ hổng/sự cố</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình sản phẩm</t>
+          <t>Kiến trúc giải pháp</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
@@ -7232,18 +7232,18 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>3.10.2.2</t>
+          <t>3.10.2.1 a)</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Quét mã độc và tắt autorun/autoplay với USB, ổ cứng, thẻ nhớ</t>
+          <t>Cài và duy trì phần mềm chống mã độc (hoặc tương đương) trên máy chủ, máy người dùng</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>GPO tắt autorun, chính sách quét</t>
+          <t>Báo cáo độ phủ agent</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
@@ -7253,28 +7253,28 @@
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Sao lưu và khôi phục dữ liệu</t>
+          <t>Phòng chống phần mềm độc hại</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>3.11.2.1 a)</t>
+          <t>3.10.2.1 b)</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Quy định sao lưu/khôi phục: loại dữ liệu (cấu hình, bản dự phòng HĐH máy chủ, CSDL, dữ liệu nghiệp vụ), tần suất, phương pháp, vùng lưu, khôi phục thử định kỳ</t>
+          <t>Tính năng tối thiểu: bảo vệ thời gian thực, tự cập nhật mẫu nhận diện</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Quy định sao lưu</t>
+          <t>Cấu hình sản phẩm</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
@@ -7284,28 +7284,28 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Sao lưu và khôi phục dữ liệu</t>
+          <t>Phòng chống phần mềm độc hại</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>3.11.2.1 b)</t>
+          <t>3.10.2.2</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy định sao lưu ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Quét mã độc và tắt autorun/autoplay với USB, ổ cứng, thẻ nhớ</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>GPO tắt autorun, chính sách quét</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
@@ -7325,18 +7325,18 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>3.11.2.2</t>
+          <t>3.11.2.1 a)</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Danh sách dữ liệu cần sao lưu và tần suất theo ngày/tuần/tháng…</t>
+          <t>Quy định sao lưu/khôi phục: loại dữ liệu (cấu hình, bản dự phòng HĐH máy chủ, CSDL, dữ liệu nghiệp vụ), tần suất, phương pháp, vùng lưu, khôi phục thử định kỳ</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr"/>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Bảng lịch sao lưu</t>
+          <t>Quy định sao lưu</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
@@ -7356,18 +7356,18 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>3.11.2.3</t>
+          <t>3.11.2.1 b)</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Bảo vệ bản sao lưu: toàn vẹn, sẵn sàng, khôi phục được</t>
+          <t>Rà soát quy định sao lưu ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình bảo vệ</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
@@ -7377,28 +7377,28 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Quản lý hạ tầng mạng</t>
+          <t>Sao lưu và khôi phục dữ liệu</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.1 a)</t>
+          <t>3.11.2.2</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Lập, duy trì sơ đồ kiến trúc mạng và hồ sơ mạng</t>
+          <t>Danh sách dữ liệu cần sao lưu và tần suất theo ngày/tuần/tháng…</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Sơ đồ mạng; biên bản thẩm tra thiết kế (cấp 4–5)</t>
+          <t>Bảng lịch sao lưu</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
@@ -7408,28 +7408,28 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Quản lý hạ tầng mạng</t>
+          <t>Sao lưu và khôi phục dữ liệu</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.1 b)</t>
+          <t>3.11.2.3</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Kiến trúc mạng an toàn theo 3 nguyên tắc: phân vùng, đặc quyền tối thiểu, sẵn sàng</t>
+          <t>Bảo vệ bản sao lưu: toàn vẹn, sẵn sàng, khôi phục được</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Tài liệu kiến trúc</t>
+          <t>Cấu hình bảo vệ</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -7449,18 +7449,18 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.1 c)</t>
+          <t>3.12.2.1 a)</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ mạng gồm: tổng quan kiến trúc, sơ đồ chi tiết, tài liệu kỹ thuật, mô tả phương án ANM</t>
+          <t>Có phương án lập và duy trì sơ đồ kiến trúc mạng và hồ sơ mạng</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Bộ hồ sơ mạng</t>
+          <t>Phương án (trong Quy chế/phương án ANM); sơ đồ mạng hiện có</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
@@ -7480,18 +7480,18 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.1 d)</t>
+          <t>3.12.2.1 b)</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật sơ đồ mạng 1 lần/năm hoặc khi thay đổi</t>
+          <t>Có phương án triển khai, duy trì kiến trúc mạng an toàn theo 3 nguyên tắc: phân vùng, đặc quyền tối thiểu, sẵn sàng</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản sơ đồ</t>
+          <t>Phương án kiến trúc mạng</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
@@ -7511,18 +7511,18 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.2</t>
+          <t>3.12.2.1 c)</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Có phương án dự phòng cho thiết bị mạng chính</t>
+          <t>Hồ sơ mạng gồm: tổng quan kiến trúc, sơ đồ chi tiết, tài liệu kỹ thuật, mô tả phương án ANM</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr"/>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Sơ đồ HA, hợp đồng kênh truyền</t>
+          <t>Bộ hồ sơ mạng</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
@@ -7542,18 +7542,18 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.2</t>
+          <t>3.12.2.1 d)</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Tường lửa có IPS (hoặc tương đương) kiểm soát giữa vùng mạng; kiểm soát thiết bị đầu cuối kết nối vào mạng</t>
+          <t>Cập nhật sơ đồ mạng 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình NGFW/IPS</t>
+          <t>Lịch sử phiên bản sơ đồ</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
@@ -7578,13 +7578,13 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật định kỳ CSDL nhận diện tấn công cho các giải pháp ANM</t>
+          <t>Có phương án dự phòng cho thiết bị mạng chính</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr"/>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Nhật ký cập nhật signature</t>
+          <t>Sơ đồ HA, hợp đồng kênh truyền</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr"/>
@@ -7609,13 +7609,13 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Quản lý thay đổi</t>
+          <t>Tường lửa có IPS (hoặc tương đương) kiểm soát giữa vùng mạng; kiểm soát thiết bị đầu cuối kết nối vào mạng</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Phiếu thay đổi (change request)</t>
+          <t>Cấu hình NGFW/IPS</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
@@ -7640,13 +7640,13 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Theo dõi hiệu năng (CPU, RAM…) để bảo đảm hoạt động bình thường</t>
+          <t>Cập nhật định kỳ CSDL nhận diện tấn công cho các giải pháp ANM</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr"/>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Dashboard giám sát</t>
+          <t>Nhật ký cập nhật signature</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
@@ -7666,18 +7666,18 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.3 a)</t>
+          <t>3.12.2.2</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Lập kế hoạch và quy trình kiểm thử, nghiệm thu (nêu rõ nội dung cần thử)</t>
+          <t>Quản lý thay đổi</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Kế hoạch thử nghiệm</t>
+          <t>Phiếu thay đổi (change request)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
@@ -7697,18 +7697,18 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.3 b)</t>
+          <t>3.12.2.2</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Kiểm thử hệ thống trước khi đưa vào vận hành</t>
+          <t>Theo dõi hiệu năng (CPU, RAM…) để bảo đảm hoạt động bình thường</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr"/>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo kiểm thử</t>
+          <t>Dashboard giám sát</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
@@ -7728,18 +7728,18 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.3 c)</t>
+          <t>3.12.2.3 a)</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Có nhân sự phụ trách thử nghiệm, nghiệm thu</t>
+          <t>Lập kế hoạch và quy trình kiểm thử, nghiệm thu (nêu rõ nội dung cần thử)</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr"/>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Quyết định phân công</t>
+          <t>Kế hoạch thử nghiệm</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr"/>
@@ -7759,18 +7759,18 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.4 a)</t>
+          <t>3.12.2.3 b)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Chỉ cho phép kết nối an toàn (nếu hỗ trợ) khi truy cập nội bộ hoặc quản trị từ xa</t>
+          <t>Kiểm thử hệ thống trước khi đưa vào vận hành</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr"/>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình SSH/TLS, tắt Telnet/HTTP</t>
+          <t>Báo cáo kiểm thử</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
@@ -7790,18 +7790,18 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.4 b)</t>
+          <t>3.12.2.3 c)</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Thiết bị phải yêu cầu đăng nhập khi quản trị tại chỗ cũng như từ xa</t>
+          <t>Có nhân sự phụ trách thử nghiệm, nghiệm thu</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình xác thực thiết bị</t>
+          <t>Quyết định phân công</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr"/>
@@ -7821,18 +7821,18 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.4 c)</t>
+          <t>3.12.2.4 a)</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Kiểm soát truy cập từ ngoài vào theo từng dịch vụ; chặn mọi truy cập không được phép</t>
+          <t>Chỉ cho phép kết nối an toàn (nếu hỗ trợ) khi truy cập nội bộ hoặc quản trị từ xa</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr"/>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Rule firewall</t>
+          <t>Cấu hình SSH/TLS, tắt Telnet/HTTP</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr"/>
@@ -7852,18 +7852,18 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.4 d)</t>
+          <t>3.12.2.4 b)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Đặt timeout tự đóng phiên kết nối không hoạt động</t>
+          <t>Thiết bị phải yêu cầu đăng nhập khi quản trị tại chỗ cũng như từ xa</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình timeout</t>
+          <t>Cấu hình xác thực thiết bị</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr"/>
@@ -7883,18 +7883,18 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>3.12.2.5</t>
+          <t>3.12.2.4 c)</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Truy cập từ xa của quản trị viên, người dùng tác nghiệp qua VPN (hoặc tương đương) có xác thực</t>
+          <t>Kiểm soát truy cập từ ngoài vào theo từng dịch vụ; chặn mọi truy cập không được phép</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình VPN/ZTNA</t>
+          <t>Rule firewall</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
@@ -7904,28 +7904,28 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
+          <t>Quản lý hạ tầng mạng</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>3.13.2.1 a)</t>
+          <t>3.12.2.4 d)</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Phân công người phụ trách vận hành, quản trị và bảo vệ ANM cho hệ thống</t>
+          <t>Đặt timeout tự đóng phiên kết nối không hoạt động</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Quyết định phân công</t>
+          <t>Cấu hình timeout</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr"/>
@@ -7935,28 +7935,28 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
+          <t>Quản lý hạ tầng mạng</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>3.13.2.1 b)</t>
+          <t>3.12.2.5</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Nhân sự có trình độ ANM/CNTT; ký cam kết bảo mật trong và sau khi nghỉ việc</t>
+          <t>Truy cập từ xa của quản trị viên, người dùng tác nghiệp qua VPN (hoặc tương đương) có xác thực</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr"/>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ năng lực, cam kết bảo mật</t>
+          <t>Cấu hình VPN/ZTNA</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
@@ -7976,18 +7976,18 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>3.13.2.2 a)</t>
+          <t>3.13.2.1 a)</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Chương trình nâng cao nhận thức ANM cho mọi người dùng HTTT</t>
+          <t>Phân công người phụ trách vận hành, quản trị và bảo vệ ANM cho hệ thống</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Tài liệu, danh sách tham dự</t>
+          <t>Quyết định phân công</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr"/>
@@ -8007,18 +8007,18 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>3.13.2.2 b)</t>
+          <t>3.13.2.1 b)</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Đào tạo nhận thức ≥ 1 lần/năm</t>
+          <t>Nhân sự có trình độ ANM/CNTT; ký cam kết bảo mật trong và sau khi nghỉ việc</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Danh sách, bài kiểm tra</t>
+          <t>Hồ sơ năng lực, cam kết bảo mật</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
@@ -8038,18 +8038,18 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>3.13.2.2 c)</t>
+          <t>3.13.2.2 a)</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Thu hồi thẻ, dữ liệu, thiết bị, tài sản khi nghỉ hoặc chuyển việc</t>
+          <t>Chương trình nâng cao nhận thức ANM cho mọi người dùng HTTT</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Biên bản bàn giao</t>
+          <t>Tài liệu, danh sách tham dự</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr"/>
@@ -8059,28 +8059,28 @@
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
+          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>3.14.1</t>
+          <t>3.13.2.2 b)</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Quy trình đánh giá nhà cung cấp dịch vụ ANM, lưu trữ/xử lý dữ liệu nhạy cảm, nền tảng quan trọng</t>
+          <t>Đào tạo nhận thức ≥ 1 lần/năm</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Quy trình đánh giá NCC</t>
+          <t>Danh sách, bài kiểm tra</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
@@ -8090,28 +8090,28 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
+          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>3.14.2</t>
+          <t>3.13.2.2 c)</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Danh sách nhà cung cấp, theo dõi trạng thái</t>
+          <t>Thu hồi thẻ, dữ liệu, thiết bị, tài sản khi nghỉ hoặc chuyển việc</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Danh sách NCC</t>
+          <t>Biên bản bàn giao</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr"/>
@@ -8131,18 +8131,18 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>3.14.2</t>
+          <t>3.14.1</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Phân loại nhà cung cấp</t>
+          <t>Quy trình đánh giá nhà cung cấp dịch vụ ANM, lưu trữ/xử lý dữ liệu nhạy cảm, nền tảng quan trọng</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Tiêu chí phân loại</t>
+          <t>Quy trình đánh giá NCC</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr"/>
@@ -8167,13 +8167,13 @@
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Văn bản phân định phạm vi trách nhiệm giữa nhà cung cấp và tổ chức</t>
+          <t>Danh sách nhà cung cấp, theo dõi trạng thái</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Hợp đồng/SLA/ma trận RACI</t>
+          <t>Danh sách NCC</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr"/>
@@ -8198,13 +8198,13 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật danh sách nhà cung cấp ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Phân loại nhà cung cấp</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Ngày cập nhật</t>
+          <t>Tiêu chí phân loại</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
@@ -8214,28 +8214,28 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.1 a)</t>
+          <t>3.14.2</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Chỉ định người chủ chốt và ít nhất một người dự phòng quản lý ứng phó sự cố</t>
+          <t>Văn bản phân định phạm vi trách nhiệm giữa nhà cung cấp và tổ chức</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Quyết định phân công</t>
+          <t>Hợp đồng/SLA/ma trận RACI</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr"/>
@@ -8245,28 +8245,28 @@
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.1 b)</t>
+          <t>3.14.2</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Đầu mối tiếp nhận báo cáo sự cố; xác minh thông tin liên hệ hằng năm</t>
+          <t>Cập nhật danh sách nhà cung cấp ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Danh bạ có ngày xác minh</t>
+          <t>Ngày cập nhật</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
@@ -8286,18 +8286,18 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.1 c)</t>
+          <t>3.15.2.1 a)</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Phân công vai trò, trách nhiệm từng thành viên đội ứng phó</t>
+          <t>Chỉ định người chủ chốt và ít nhất một người dự phòng quản lý ứng phó sự cố</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Bảng RACI đội ứng phó</t>
+          <t>Quyết định phân công</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr"/>
@@ -8317,18 +8317,18 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.1 d)</t>
+          <t>3.15.2.1 b)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Quy định trách nhiệm phối hợp của các phòng ban với đội ứng phó</t>
+          <t>Đầu mối tiếp nhận báo cáo sự cố; xác minh thông tin liên hệ hằng năm</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Quy chế phối hợp</t>
+          <t>Danh bạ có ngày xác minh</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr"/>
@@ -8348,18 +8348,18 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.2 a)</t>
+          <t>3.15.2.1 c)</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Quy trình báo cáo sự cố nội bộ</t>
+          <t>Phân công vai trò, trách nhiệm từng thành viên đội ứng phó</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Quy trình, mẫu báo cáo</t>
+          <t>Bảng RACI đội ứng phó</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr"/>
@@ -8379,18 +8379,18 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.2 b)</t>
+          <t>3.15.2.1 d)</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Phân nhóm sự cố ANM</t>
+          <t>Quy định trách nhiệm phối hợp của các phòng ban với đội ứng phó</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Bảng phân loại sự cố</t>
+          <t>Quy chế phối hợp</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr"/>
@@ -8410,18 +8410,18 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.2 c)</t>
+          <t>3.15.2.2 a)</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật quy trình báo cáo ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Quy trình báo cáo sự cố nội bộ</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Quy trình, mẫu báo cáo</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr"/>
@@ -8441,18 +8441,18 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.3 a)</t>
+          <t>3.15.2.2 b)</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Quy trình ứng phó có cơ chế phối hợp với cơ quan chức năng, chuyên gia, nhà cung cấp dịch vụ</t>
+          <t>Phân nhóm sự cố ANM</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Quy trình ứng phó</t>
+          <t>Bảng phân loại sự cố</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr"/>
@@ -8472,12 +8472,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>3.15.2.3 b)</t>
+          <t>3.15.2.2 c)</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật quy trình ứng phó ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Cập nhật quy trình báo cáo ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr"/>
@@ -8490,9 +8490,71 @@
       <c r="H113" s="11" t="inlineStr"/>
       <c r="I113" s="11" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>3.15.2.3 a)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>Quy trình ứng phó có cơ chế phối hợp với cơ quan chức năng, chuyên gia, nhà cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr"/>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>Quy trình ứng phó</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="11" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>3.15.2.3 b)</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Cập nhật quy trình ứng phó ≥ 1 lần/năm hoặc khi thay đổi</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr"/>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>Lịch sử phiên bản</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I113"/>
-  <conditionalFormatting sqref="E5:E113">
+  <autoFilter ref="A4:I115"/>
+  <conditionalFormatting sqref="E5:E115">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Đạt"</formula>
     </cfRule>
@@ -8507,7 +8569,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: Đạt, Một phần, Chưa hoặc N/A" type="list">
+    <dataValidation sqref="E5:E115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: Đạt, Một phần, Chưa hoặc N/A" type="list">
       <formula1>"Đạt,Một phần,Chưa,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8522,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9771,13 +9833,13 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Quy trình, công cụ cấp/thu hồi quyền cho 4 loại tài khoản (quản trị, tác nghiệp, kỹ thuật, dịch vụ) theo vai trò</t>
+          <t>Có quy trình, công cụ phân quyền và quản lý quyền truy cập cho 4 loại tài khoản (quản trị, tác nghiệp, kỹ thuật, dịch vụ)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Quy trình quản lý tài khoản</t>
+          <t>Quy trình quản lý tài khoản, công cụ quản lý tập trung</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
@@ -9797,18 +9859,18 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>4.6.1 c)</t>
+          <t>4.6.1 b)</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>Ghi log và giám sát hoạt động của tài khoản người dùng</t>
+          <t>Quy trình tạo, gán, quản lý, thu hồi đặc quyền và quyền truy cập; quyền của từng loại tài khoản nhất quán theo vai trò, chỉ đủ cho dữ liệu, tài sản cần thiết</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình audit log đăng nhập</t>
+          <t>Quy trình cấp/thu hồi quyền, phiếu yêu cầu đã duyệt</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
@@ -9828,18 +9890,18 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.1 a)</t>
+          <t>4.6.1 c)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Danh sách mọi tài khoản trên phần cứng và phần mềm</t>
+          <t>Ghi log và giám sát hoạt động của tài khoản người dùng</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Danh sách tài khoản</t>
+          <t>Cấu hình audit log đăng nhập</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr"/>
@@ -9859,25 +9921,21 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.1 b)</t>
+          <t>4.6.2.1 a)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Danh sách gồm tối thiểu: tài khoản quản trị, tác nghiệp, kỹ thuật</t>
+          <t>Danh sách mọi tài khoản trên phần cứng và phần mềm</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Danh sách tài khoản phân loại</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Danh sách tài khoản</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr"/>
     </row>
@@ -9894,21 +9952,25 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.1 c)</t>
+          <t>4.6.2.1 b)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Trường tối thiểu: loại, tên, trạng thái, hệ thống, người quản lý, phòng ban, ngày kích hoạt/vô hiệu; không còn tài khoản không hợp lệ</t>
+          <t>Danh sách gồm tối thiểu: tài khoản quản trị, tác nghiệp, kỹ thuật</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Danh sách có đủ trường</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
+          <t>Danh sách tài khoản phân loại</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H45" s="11" t="inlineStr"/>
       <c r="I45" s="11" t="inlineStr"/>
     </row>
@@ -9925,18 +9987,18 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.1 d)</t>
+          <t>4.6.2.1 c)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Rà soát danh sách tài khoản ≥ 1 lần/năm</t>
+          <t>Trường tối thiểu: loại, tên, trạng thái, hệ thống, người quản lý, phòng ban, ngày kích hoạt/vô hiệu; không còn tài khoản không hợp lệ</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Biên bản rà soát</t>
+          <t>Danh sách có đủ trường</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
@@ -9956,25 +10018,21 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.2 a)</t>
+          <t>4.6.2.1 d)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình bắt đổi mật khẩu mặc định; quy tắc độ dài, loại ký tự; thời hạn đổi và thời hạn hiệu lực mật khẩu</t>
+          <t>Rà soát danh sách tài khoản ≥ 1 lần/năm</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Chính sách mật khẩu (GPO/IdP)</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Biên bản rà soát</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr"/>
     </row>
@@ -9991,21 +10049,25 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.2 b)</t>
+          <t>4.6.2.2 a)</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Gợi ý: mật khẩu riêng cho từng tài sản hoặc xác thực tập trung; bắt đổi ở lần đăng nhập đầu</t>
+          <t>Cấu hình bắt đổi mật khẩu mặc định; quy tắc độ dài, loại ký tự; thời hạn đổi và thời hạn hiệu lực mật khẩu</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình IdP/SSO</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
+          <t>Chính sách mật khẩu (GPO/IdP)</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H48" s="11" t="inlineStr"/>
       <c r="I48" s="11" t="inlineStr"/>
     </row>
@@ -10027,13 +10089,13 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Gợi ý độ dài: ≥ 8 ký tự nếu có MFA; ≥ 14 ký tự gồm đủ 4 loại ký tự nếu không có MFA</t>
+          <t>Gợi ý: mật khẩu riêng cho từng tài sản hoặc xác thực tập trung; bắt đổi ở lần đăng nhập đầu</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Chính sách mật khẩu</t>
+          <t>Cấu hình IdP/SSO</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
@@ -10058,13 +10120,13 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Tài khoản quản trị đổi mật khẩu ít nhất 2 tháng/lần</t>
+          <t>Gợi ý độ dài: ≥ 8 ký tự nếu có MFA; ≥ 14 ký tự gồm đủ 4 loại ký tự nếu không có MFA</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Chính sách hết hạn mật khẩu tài khoản quản trị</t>
+          <t>Chính sách mật khẩu</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
@@ -10084,18 +10146,18 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.3</t>
+          <t>4.6.2.2 b)</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Đổi hoặc vô hiệu hóa tài khoản mặc định (root, administrator, tài khoản cài sẵn của hãng)</t>
+          <t>Tài khoản quản trị đổi mật khẩu ít nhất 2 tháng/lần</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Danh sách tài khoản mặc định đã xử lý</t>
+          <t>Chính sách hết hạn mật khẩu tài khoản quản trị</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
@@ -10120,13 +10182,13 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Tách biệt quản lý 4 loại tài khoản</t>
+          <t>Đổi hoặc vô hiệu hóa tài khoản mặc định (root, administrator, tài khoản cài sẵn của hãng)</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>Quy định + danh sách phân loại</t>
+          <t>Danh sách tài khoản mặc định đã xử lý</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
@@ -10151,13 +10213,13 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Mỗi tài khoản gắn một người; dùng chung phải được phê duyệt và truy vết được người dùng từng thời điểm</t>
+          <t>Tách biệt quản lý 4 loại tài khoản</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Phê duyệt tài khoản dùng chung, sổ theo dõi</t>
+          <t>Quy định + danh sách phân loại</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
@@ -10182,13 +10244,13 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Xóa/vô hiệu hóa tài khoản không hoạt động quá 45 ngày hoặc ngay khi đổi nhân sự</t>
+          <t>Mỗi tài khoản gắn một người; dùng chung phải được phê duyệt và truy vết được người dùng từng thời điểm</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo tài khoản inactive</t>
+          <t>Phê duyệt tài khoản dùng chung, sổ theo dõi</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
@@ -10213,13 +10275,13 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy định quản lý tài khoản ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Xóa/vô hiệu hóa tài khoản không hoạt động quá 45 ngày hoặc ngay khi đổi nhân sự</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Báo cáo tài khoản inactive</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr"/>
@@ -10239,18 +10301,18 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>4.6.2.4</t>
+          <t>4.6.2.3</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Áp dụng đặc quyền tối thiểu và phân tách nhiệm vụ cho mọi loại tài khoản</t>
+          <t>Rà soát quy định quản lý tài khoản ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr"/>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Ma trận vai trò – quyền</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr"/>
@@ -10275,13 +10337,13 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Tài liệu hóa quyền cần thiết theo chức danh, bộ phận</t>
+          <t>Áp dụng đặc quyền tối thiểu và phân tách nhiệm vụ cho mọi loại tài khoản</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr"/>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Ma trận quyền theo chức danh</t>
+          <t>Ma trận vai trò – quyền</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
@@ -10306,13 +10368,13 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>MFA cho truy cập từ ngoài tổ chức, từ đối tác/bên thứ ba, từ Internet và cho tài khoản quản trị</t>
+          <t>Tài liệu hóa quyền cần thiết theo chức danh, bộ phận</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr"/>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình MFA</t>
+          <t>Ma trận quyền theo chức danh</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
@@ -10337,13 +10399,13 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy định quản lý truy cập ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>MFA cho truy cập từ ngoài tổ chức, từ đối tác/bên thứ ba, từ Internet và cho tài khoản quản trị</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Cấu hình MFA</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
@@ -10353,28 +10415,28 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Quản lý lỗ hổng bảo mật</t>
+          <t>Quản lý tài khoản và quyền truy cập</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>4.7.1 b)</t>
+          <t>4.6.2.4</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Theo dõi thông tin mối đe dọa, lỗ hổng mới từ nhiều nguồn</t>
+          <t>Rà soát quy định quản lý truy cập ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Nguồn tin đăng ký (NCSC, CVE, hãng…)</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
@@ -10394,18 +10456,18 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>4.7.2.1 a)</t>
+          <t>4.7.1 a)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Quy trình quản lý lỗ hổng: rà quét phát hiện, chấm mức nghiêm trọng, chia sẻ/tiếp nhận báo cáo, khắc phục theo ưu tiên và kiểm tra lại</t>
+          <t>Xây dựng, phát triển kế hoạch đánh giá, theo dõi lỗ hổng thường xuyên để khắc phục và giảm nguy cơ bị tấn công</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr"/>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Quy trình quản lý lỗ hổng</t>
+          <t>Kế hoạch đánh giá lỗ hổng (phạm vi, lịch rà quét)</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr"/>
@@ -10425,18 +10487,18 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>4.7.2.1 b)</t>
+          <t>4.7.1 b)</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy trình và thực hiện rà quét lỗ hổng ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Theo dõi thông tin mối đe dọa, lỗ hổng mới từ nhiều nguồn</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr"/>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo rà quét, biên bản rà soát</t>
+          <t>Nguồn tin đăng ký (NCSC, CVE, hãng…)</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr"/>
@@ -10456,25 +10518,21 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>4.7.2.2</t>
+          <t>4.7.2.1 a)</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Có phương án vá cho toàn bộ phần cứng, phần mềm của HTTT</t>
+          <t>Quy trình quản lý lỗ hổng: rà quét phát hiện, chấm mức nghiêm trọng, chia sẻ/tiếp nhận báo cáo, khắc phục theo ưu tiên và kiểm tra lại</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr"/>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Kế hoạch vá</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Quy trình quản lý lỗ hổng</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="11" t="inlineStr"/>
       <c r="I63" s="11" t="inlineStr"/>
     </row>
@@ -10491,25 +10549,21 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>4.7.2.2</t>
+          <t>4.7.2.1 b)</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Trước khi vá hệ thống có dữ liệu quan trọng: đánh giá tác động, thử nghiệm, có phương án khôi phục</t>
+          <t>Rà soát quy trình và thực hiện rà quét lỗ hổng ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr"/>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Biên bản thử nghiệm bản vá</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Báo cáo rà quét, biên bản rà soát</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr"/>
       <c r="H64" s="11" t="inlineStr"/>
       <c r="I64" s="11" t="inlineStr"/>
     </row>
@@ -10531,16 +10585,20 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Kiểm tra, cập nhật bản vá HĐH và ứng dụng cho máy tính, di động cấp cho người dùng ≥ 1 lần/tháng</t>
+          <t>Có phương án vá cho toàn bộ phần cứng, phần mềm của HTTT</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo tuân thủ bản vá hằng tháng</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
+          <t>Kế hoạch vá</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H65" s="11" t="inlineStr"/>
       <c r="I65" s="11" t="inlineStr"/>
     </row>
@@ -10562,44 +10620,48 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Giám sát để phát hiện lỗ hổng mới và vá kịp thời</t>
+          <t>Trước khi vá hệ thống có dữ liệu quan trọng: đánh giá tác động, thử nghiệm, có phương án khôi phục</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Nhật ký vá</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr"/>
+          <t>Biên bản thử nghiệm bản vá</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H66" s="11" t="inlineStr"/>
       <c r="I66" s="11" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhật ký an ninh mạng</t>
+          <t>Quản lý lỗ hổng bảo mật</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>4.8.2.1 a)</t>
+          <t>4.7.2.2</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Quy định quản lý log: cách ghi, thu thập, kiểm tra, lưu trữ</t>
+          <t>Kiểm tra, cập nhật bản vá HĐH và ứng dụng cho máy tính, di động cấp cho người dùng ≥ 1 lần/tháng</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Quy định quản lý nhật ký</t>
+          <t>Báo cáo tuân thủ bản vá hằng tháng</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
@@ -10609,35 +10671,31 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhật ký an ninh mạng</t>
+          <t>Quản lý lỗ hổng bảo mật</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>4.8.2.1 a)</t>
+          <t>4.7.2.2</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Thu thập tối thiểu: log truy cập hệ thống, log ứng dụng, log cảnh báo thiết bị bảo mật</t>
+          <t>Giám sát để phát hiện lỗ hổng mới và vá kịp thời</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Danh sách nguồn log</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Nhật ký vá</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr"/>
       <c r="H68" s="11" t="inlineStr"/>
       <c r="I68" s="11" t="inlineStr"/>
     </row>
@@ -10659,20 +10717,16 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Log truy cập có nguồn, đích, tài khoản, thời điểm, hành vi; log cảnh báo có tên, thiết bị, mức độ, nguồn, loại, thời điểm</t>
+          <t>Quy định quản lý log: cách ghi, thu thập, kiểm tra, lưu trữ</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr"/>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Mẫu bản ghi log</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Quy định quản lý nhật ký</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="11" t="inlineStr"/>
       <c r="I69" s="11" t="inlineStr"/>
     </row>
@@ -10694,16 +10748,20 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Đồng bộ thời gian qua máy chủ thời gian (NTP) cho mọi thành phần tham gia giám sát</t>
+          <t>Thu thập tối thiểu: log truy cập hệ thống, log ứng dụng, log cảnh báo thiết bị bảo mật</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình NTP</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
+          <t>Danh sách nguồn log</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H70" s="11" t="inlineStr"/>
       <c r="I70" s="11" t="inlineStr"/>
     </row>
@@ -10725,13 +10783,13 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Bảo đảm dung lượng lưu log tối thiểu 1 tháng</t>
+          <t>Log truy cập có nguồn, đích, tài khoản, thời điểm, hành vi; log cảnh báo có tên, thiết bị, mức độ, nguồn, loại, thời điểm</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình retention, ảnh chụp dung lượng</t>
+          <t>Mẫu bản ghi log</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -10760,13 +10818,13 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Rà soát log ANM ≥ 1 lần/năm</t>
+          <t>Đồng bộ thời gian qua máy chủ thời gian (NTP) cho mọi thành phần tham gia giám sát</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Biên bản rà soát log</t>
+          <t>Cấu hình NTP</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
@@ -10786,49 +10844,53 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>4.8.2.1 b)</t>
+          <t>4.8.2.1 a)</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Kiểm tra, cập nhật quy trình quản lý log ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Bảo đảm dung lượng lưu log tối thiểu 1 tháng</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
+          <t>Cấu hình retention, ảnh chụp dung lượng</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H73" s="11" t="inlineStr"/>
       <c r="I73" s="11" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Bảo vệ trình duyệt web, thư điện tử</t>
+          <t>Quản lý nhật ký an ninh mạng</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>4.9.2.1 a)</t>
+          <t>4.8.2.1 a)</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Danh sách trình duyệt và dịch vụ email được phép</t>
+          <t>Rà soát log ANM ≥ 1 lần/năm</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Danh sách được phép</t>
+          <t>Biên bản rà soát log</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
@@ -10838,28 +10900,28 @@
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Bảo vệ trình duyệt web, thư điện tử</t>
+          <t>Quản lý nhật ký an ninh mạng</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>4.9.2.1 b)</t>
+          <t>4.8.2.1 b)</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Chỉ dùng phiên bản còn được hãng hỗ trợ</t>
+          <t>Kiểm tra, cập nhật quy trình quản lý log ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo phiên bản</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
@@ -10879,18 +10941,18 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>4.9.2.1 c)</t>
+          <t>4.9.2.1 a)</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật bản vá trình duyệt, email thường xuyên (hoặc biện pháp tương đương)</t>
+          <t>Danh sách trình duyệt và dịch vụ email được phép</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr"/>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo bản vá</t>
+          <t>Danh sách được phép</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr"/>
@@ -10910,18 +10972,18 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>4.9.2.2</t>
+          <t>4.9.2.1 b)</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Dùng dịch vụ lọc tên miền (DNS filtering) chặn tên miền giả mạo, độc hại</t>
+          <t>Chỉ dùng phiên bản còn được hãng hỗ trợ</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr"/>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình DNS filtering</t>
+          <t>Báo cáo phiên bản</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
@@ -10931,28 +10993,28 @@
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Phòng chống phần mềm độc hại</t>
+          <t>Bảo vệ trình duyệt web, thư điện tử</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>4.10.1 a)</t>
+          <t>4.9.2.1 c)</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Quy định phòng, chống, khắc phục mã độc</t>
+          <t>Cập nhật bản vá trình duyệt, email thường xuyên (hoặc biện pháp tương đương)</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr"/>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Quy định phòng chống mã độc</t>
+          <t>Báo cáo bản vá</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
@@ -10962,28 +11024,28 @@
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Phòng chống phần mềm độc hại</t>
+          <t>Bảo vệ trình duyệt web, thư điện tử</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>4.10.1 b)</t>
+          <t>4.9.2.2</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Chống mã độc cho mọi tài sản và điểm kết nối (trong và ngoài); tự quét, chặn, cập nhật mẫu, gắn với quy trình lỗ hổng/sự cố</t>
+          <t>Dùng dịch vụ lọc tên miền (DNS filtering) chặn tên miền giả mạo, độc hại</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr"/>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Kiến trúc giải pháp</t>
+          <t>Cấu hình DNS filtering</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -11003,18 +11065,18 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>4.10.2.1 a)</t>
+          <t>4.10.1 a)</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>Cài và duy trì phần mềm chống mã độc (hoặc tương đương) trên máy chủ, máy người dùng</t>
+          <t>Quy định phòng, chống, khắc phục mã độc</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo độ phủ agent</t>
+          <t>Quy định phòng chống mã độc</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
@@ -11034,18 +11096,18 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>4.10.2.1 b)</t>
+          <t>4.10.1 b)</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Tính năng tối thiểu: bảo vệ thời gian thực, tự cập nhật mẫu nhận diện</t>
+          <t>Chống mã độc cho mọi tài sản và điểm kết nối (trong và ngoài); tự quét, chặn, cập nhật mẫu, gắn với quy trình lỗ hổng/sự cố</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình sản phẩm</t>
+          <t>Kiến trúc giải pháp</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>
@@ -11065,18 +11127,18 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>4.10.2.2</t>
+          <t>4.10.2.1 a)</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Quét mã độc và tắt autorun/autoplay với USB, ổ cứng, thẻ nhớ</t>
+          <t>Cài và duy trì phần mềm chống mã độc (hoặc tương đương) trên máy chủ, máy người dùng</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr"/>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>GPO tắt autorun, chính sách quét</t>
+          <t>Báo cáo độ phủ agent</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
@@ -11086,28 +11148,28 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Sao lưu và khôi phục dữ liệu</t>
+          <t>Phòng chống phần mềm độc hại</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>4.11.2.1 a)</t>
+          <t>4.10.2.1 b)</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Quy định sao lưu/khôi phục: loại dữ liệu (cấu hình, bản dự phòng HĐH máy chủ, CSDL, dữ liệu nghiệp vụ), tần suất, phương pháp, vùng lưu, khôi phục thử định kỳ</t>
+          <t>Tính năng tối thiểu: bảo vệ thời gian thực, tự cập nhật mẫu nhận diện</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Quy định sao lưu</t>
+          <t>Cấu hình sản phẩm</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
@@ -11117,28 +11179,28 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Sao lưu và khôi phục dữ liệu</t>
+          <t>Phòng chống phần mềm độc hại</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>4.11.2.1 b)</t>
+          <t>4.10.2.2</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Rà soát quy định sao lưu ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Quét mã độc và tắt autorun/autoplay với USB, ổ cứng, thẻ nhớ</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr"/>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>GPO tắt autorun, chính sách quét</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr"/>
@@ -11158,18 +11220,18 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>4.11.2.2</t>
+          <t>4.11.2.1 a)</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Danh sách dữ liệu cần sao lưu và tần suất theo ngày/tuần/tháng…</t>
+          <t>Quy định sao lưu/khôi phục: loại dữ liệu (cấu hình, bản dự phòng HĐH máy chủ, CSDL, dữ liệu nghiệp vụ), tần suất, phương pháp, vùng lưu, khôi phục thử định kỳ</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr"/>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Bảng lịch sao lưu</t>
+          <t>Quy định sao lưu</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
@@ -11189,18 +11251,18 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>4.11.2.3</t>
+          <t>4.11.2.1 b)</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>Bảo vệ bản sao lưu: toàn vẹn, sẵn sàng, khôi phục được</t>
+          <t>Rà soát quy định sao lưu ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr"/>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình bảo vệ</t>
+          <t>Lịch sử phiên bản</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
@@ -11220,53 +11282,49 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>4.11.2.4</t>
+          <t>4.11.2.2</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Định danh, quản lý phiên bản bản sao lưu; lưu trên hạ tầng tách biệt môi trường vận hành</t>
+          <t>Danh sách dữ liệu cần sao lưu và tần suất theo ngày/tuần/tháng…</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr"/>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Sơ đồ hạ tầng backup</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Bảng lịch sao lưu</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Quản lý hạ tầng mạng</t>
+          <t>Sao lưu và khôi phục dữ liệu</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.1 a)</t>
+          <t>4.11.2.3</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>Lập, duy trì sơ đồ kiến trúc mạng và hồ sơ mạng</t>
+          <t>Bảo vệ bản sao lưu: toàn vẹn, sẵn sàng, khôi phục được</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr"/>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Sơ đồ mạng; biên bản thẩm tra thiết kế (cấp 4–5)</t>
+          <t>Cấu hình bảo vệ</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
@@ -11276,31 +11334,35 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Quản lý hạ tầng mạng</t>
+          <t>Sao lưu và khôi phục dữ liệu</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.1 b)</t>
+          <t>4.11.2.4</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Kiến trúc mạng an toàn theo 3 nguyên tắc: phân vùng, đặc quyền tối thiểu, sẵn sàng</t>
+          <t>Định danh, quản lý phiên bản bản sao lưu; lưu trên hạ tầng tách biệt môi trường vận hành</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr"/>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Tài liệu kiến trúc</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr"/>
+          <t>Sơ đồ hạ tầng backup</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H89" s="11" t="inlineStr"/>
       <c r="I89" s="11" t="inlineStr"/>
     </row>
@@ -11317,21 +11379,25 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.1 c)</t>
+          <t>4.12.2.1 a)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ mạng gồm: tổng quan kiến trúc, sơ đồ chi tiết, tài liệu kỹ thuật, mô tả phương án ANM</t>
+          <t>Thiết lập và duy trì thực tế sơ đồ kiến trúc mạng và hồ sơ mạng</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr"/>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Bộ hồ sơ mạng</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr"/>
+          <t>Sơ đồ mạng hiện hành, hồ sơ mạng</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1 (cấp 1 chỉ yêu cầu có phương án)</t>
+        </is>
+      </c>
       <c r="H90" s="11" t="inlineStr"/>
       <c r="I90" s="11" t="inlineStr"/>
     </row>
@@ -11348,23 +11414,23 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.1 d)</t>
+          <t>4.12.2.1 b)</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Khi đổi thiết kế, đánh giá lại sự phù hợp với yêu cầu an toàn</t>
+          <t>Triển khai, duy trì kiến trúc mạng an toàn theo 3 nguyên tắc: phân vùng, đặc quyền tối thiểu, sẵn sàng</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr"/>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Biên bản đánh giá thay đổi</t>
+          <t>Tài liệu kiến trúc, cấu hình phân vùng</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>Mới/khác so với cấp 1</t>
+          <t>Mới/khác so với cấp 1 (cấp 1 chỉ yêu cầu có phương án)</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr"/>
@@ -11383,18 +11449,18 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.1 e)</t>
+          <t>4.12.2.1 c)</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật sơ đồ mạng 1 lần/năm hoặc khi thay đổi</t>
+          <t>Hồ sơ mạng gồm: tổng quan kiến trúc, sơ đồ chi tiết, tài liệu kỹ thuật, mô tả phương án ANM</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr"/>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản sơ đồ</t>
+          <t>Bộ hồ sơ mạng</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr"/>
@@ -11414,21 +11480,25 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.2 a)</t>
+          <t>4.12.2.1 d)</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Có phương án dự phòng cho thiết bị mạng chính</t>
+          <t>Khi đổi thiết kế, đánh giá lại sự phù hợp với yêu cầu an toàn</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr"/>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Sơ đồ HA, hợp đồng kênh truyền</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr"/>
+          <t>Biên bản đánh giá thay đổi</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H93" s="11" t="inlineStr"/>
       <c r="I93" s="11" t="inlineStr"/>
     </row>
@@ -11445,18 +11515,18 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.2 a)</t>
+          <t>4.12.2.1 e)</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Tường lửa có IPS (hoặc tương đương) kiểm soát truy cập, chống xâm nhập giữa các vùng mạng</t>
+          <t>Cập nhật sơ đồ mạng 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình NGFW/IPS</t>
+          <t>Lịch sử phiên bản sơ đồ</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr"/>
@@ -11481,20 +11551,16 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>WAF (hoặc tương đương) cho ứng dụng web (nếu có)</t>
+          <t>Có phương án dự phòng cho thiết bị mạng chính</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr"/>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình WAF</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Sơ đồ HA, hợp đồng kênh truyền</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
       <c r="H95" s="11" t="inlineStr"/>
       <c r="I95" s="11" t="inlineStr"/>
     </row>
@@ -11516,13 +11582,13 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật định kỳ CSDL nhận diện tấn công cho các giải pháp ANM</t>
+          <t>Tường lửa có IPS (hoặc tương đương) kiểm soát truy cập, chống xâm nhập giữa các vùng mạng</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr"/>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Nhật ký cập nhật signature</t>
+          <t>Cấu hình NGFW/IPS</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
@@ -11547,16 +11613,20 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Quản lý thay đổi</t>
+          <t>WAF (hoặc tương đương) cho ứng dụng web (nếu có)</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Phiếu thay đổi (change request)</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
+          <t>Cấu hình WAF</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H97" s="11" t="inlineStr"/>
       <c r="I97" s="11" t="inlineStr"/>
     </row>
@@ -11578,13 +11648,13 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>Theo dõi hiệu năng (CPU, RAM…) để bảo đảm hoạt động bình thường</t>
+          <t>Cập nhật định kỳ CSDL nhận diện tấn công cho các giải pháp ANM</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Dashboard giám sát</t>
+          <t>Nhật ký cập nhật signature</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr"/>
@@ -11604,25 +11674,21 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.2 b)</t>
+          <t>4.12.2.2 a)</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Phân vùng tối thiểu: máy chủ, DMZ, không dây (nếu có), nội bộ, biên</t>
+          <t>Quản lý thay đổi</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Sơ đồ phân vùng, ACL giữa vùng</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Phiếu thay đổi (change request)</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
       <c r="H99" s="11" t="inlineStr"/>
       <c r="I99" s="11" t="inlineStr"/>
     </row>
@@ -11639,18 +11705,18 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.3 a)</t>
+          <t>4.12.2.2 a)</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Lập kế hoạch và quy trình kiểm thử, nghiệm thu (nêu rõ nội dung cần thử)</t>
+          <t>Theo dõi hiệu năng (CPU, RAM…) để bảo đảm hoạt động bình thường</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr"/>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Kế hoạch thử nghiệm</t>
+          <t>Dashboard giám sát</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr"/>
@@ -11670,21 +11736,25 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.3 b)</t>
+          <t>4.12.2.2 b)</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Kiểm thử hệ thống trước khi đưa vào vận hành</t>
+          <t>Phân vùng tối thiểu: máy chủ, DMZ, không dây (nếu có), nội bộ, biên</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo kiểm thử</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr"/>
+          <t>Sơ đồ phân vùng, ACL giữa vùng</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H101" s="11" t="inlineStr"/>
       <c r="I101" s="11" t="inlineStr"/>
     </row>
@@ -11701,18 +11771,18 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.3 c)</t>
+          <t>4.12.2.3 a)</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Có nhân sự phụ trách thử nghiệm, nghiệm thu</t>
+          <t>Lập kế hoạch và quy trình kiểm thử, nghiệm thu (nêu rõ nội dung cần thử)</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr"/>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Quyết định phân công</t>
+          <t>Kế hoạch thử nghiệm</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr"/>
@@ -11732,18 +11802,18 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.4 a)</t>
+          <t>4.12.2.3 b)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Chỉ cho phép kết nối an toàn (nếu hỗ trợ) khi truy cập nội bộ hoặc quản trị từ xa</t>
+          <t>Kiểm thử hệ thống trước khi đưa vào vận hành</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình SSH/TLS, tắt Telnet/HTTP</t>
+          <t>Báo cáo kiểm thử</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr"/>
@@ -11763,18 +11833,18 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.4 b)</t>
+          <t>4.12.2.3 c)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Kiểm soát truy cập từ ngoài vào theo từng dịch vụ; chặn mọi truy cập không được phép</t>
+          <t>Có nhân sự phụ trách thử nghiệm, nghiệm thu</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr"/>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Rule firewall</t>
+          <t>Quyết định phân công</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr"/>
@@ -11794,25 +11864,21 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.4 c)</t>
+          <t>4.12.2.4 a)</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Giới hạn dải địa chỉ/thiết bị được phép quản trị từ xa</t>
+          <t>Chỉ cho phép kết nối an toàn (nếu hỗ trợ) khi truy cập nội bộ hoặc quản trị từ xa</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr"/>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>ACL quản trị</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Cấu hình SSH/TLS, tắt Telnet/HTTP</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr"/>
       <c r="H105" s="11" t="inlineStr"/>
       <c r="I105" s="11" t="inlineStr"/>
     </row>
@@ -11829,18 +11895,18 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.4 d)</t>
+          <t>4.12.2.4 b)</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Đặt timeout tự đóng phiên kết nối không hoạt động</t>
+          <t>Kiểm soát truy cập từ ngoài vào theo từng dịch vụ; chặn mọi truy cập không được phép</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr"/>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình timeout</t>
+          <t>Rule firewall</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr"/>
@@ -11860,21 +11926,25 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.5</t>
+          <t>4.12.2.4 c)</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Truy cập từ xa của quản trị viên, người dùng tác nghiệp qua VPN (hoặc tương đương) có xác thực</t>
+          <t>Giới hạn dải địa chỉ/thiết bị được phép quản trị từ xa</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr"/>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình VPN/ZTNA</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr"/>
+          <t>ACL quản trị</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H107" s="11" t="inlineStr"/>
       <c r="I107" s="11" t="inlineStr"/>
     </row>
@@ -11891,25 +11961,21 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>4.12.2.5</t>
+          <t>4.12.2.4 d)</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
         <is>
-          <t>Xác thực khi kết nối từ xa và xác thực bổ sung trước khi vào hệ thống</t>
+          <t>Đặt timeout tự đóng phiên kết nối không hoạt động</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr"/>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Cấu hình MFA VPN</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Cấu hình timeout</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr"/>
       <c r="H108" s="11" t="inlineStr"/>
       <c r="I108" s="11" t="inlineStr"/>
     </row>
@@ -11931,20 +11997,16 @@
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Thiết bị truy cập từ xa phải có chống mã độc và cấu hình theo chính sách của tổ chức</t>
+          <t>Truy cập từ xa của quản trị viên, người dùng tác nghiệp qua VPN (hoặc tương đương) có xác thực</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr"/>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Chính sách posture check</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Cấu hình VPN/ZTNA</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr"/>
       <c r="H109" s="11" t="inlineStr"/>
       <c r="I109" s="11" t="inlineStr"/>
     </row>
@@ -11966,13 +12028,13 @@
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Chỉ cho phép một số địa chỉ được quản trị thiết bị từ xa (nếu hỗ trợ)</t>
+          <t>Xác thực khi kết nối từ xa và xác thực bổ sung trước khi vào hệ thống</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr"/>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>ACL quản trị</t>
+          <t>Cấu hình MFA VPN</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -11986,28 +12048,28 @@
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
+          <t>Quản lý hạ tầng mạng</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>4.13.1 a)</t>
+          <t>4.12.2.5</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Các bộ phận vận hành, quản trị, bảo vệ ANM độc lập về chuyên môn</t>
+          <t>Thiết bị truy cập từ xa phải có chống mã độc và cấu hình theo chính sách của tổ chức</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr"/>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Quy chế phân định nhiệm vụ</t>
+          <t>Chính sách posture check</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -12021,31 +12083,35 @@
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
+          <t>Quản lý hạ tầng mạng</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>4.13.2.1 a)</t>
+          <t>4.12.2.5</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
         <is>
-          <t>Phân công người phụ trách vận hành, quản trị và bảo vệ ANM cho hệ thống</t>
+          <t>Chỉ cho phép một số địa chỉ được quản trị thiết bị từ xa (nếu hỗ trợ)</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr"/>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Quyết định phân công</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr"/>
+          <t>ACL quản trị</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H112" s="11" t="inlineStr"/>
       <c r="I112" s="11" t="inlineStr"/>
     </row>
@@ -12062,21 +12128,25 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>4.13.2.1 b)</t>
+          <t>4.13.1 a)</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Nhân sự có trình độ ANM/CNTT; ký cam kết bảo mật trong và sau khi nghỉ việc</t>
+          <t>Các bộ phận vận hành, quản trị, bảo vệ ANM độc lập về chuyên môn</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr"/>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Hồ sơ năng lực, cam kết bảo mật</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr"/>
+          <t>Quy chế phân định nhiệm vụ</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H113" s="11" t="inlineStr"/>
       <c r="I113" s="11" t="inlineStr"/>
     </row>
@@ -12093,21 +12163,25 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>4.13.2.2 a)</t>
+          <t>4.13.2.1 a)</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
         <is>
-          <t>Chương trình nâng cao nhận thức ANM cho mọi người dùng HTTT</t>
+          <t>Có bộ phận (không chỉ cá nhân) phụ trách vận hành, quản trị hệ thống và bảo vệ ANM, có nhân sự cụ thể</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr"/>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Tài liệu, danh sách tham dự</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr"/>
+          <t>Quyết định giao nhiệm vụ cho bộ phận, danh sách nhân sự</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H114" s="11" t="inlineStr"/>
       <c r="I114" s="11" t="inlineStr"/>
     </row>
@@ -12124,18 +12198,18 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>4.13.2.2 b)</t>
+          <t>4.13.2.1 b)</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Đào tạo nhận thức ≥ 1 lần/năm</t>
+          <t>Nhân sự có trình độ ANM/CNTT; ký cam kết bảo mật trong và sau khi nghỉ việc</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr"/>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Danh sách, bài kiểm tra</t>
+          <t>Hồ sơ năng lực, cam kết bảo mật</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr"/>
@@ -12155,18 +12229,18 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>4.13.2.2 c)</t>
+          <t>4.13.2.2 a)</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
         <is>
-          <t>Thu hồi thẻ, dữ liệu, thiết bị, tài sản khi nghỉ hoặc chuyển việc</t>
+          <t>Chương trình nâng cao nhận thức ANM cho mọi người dùng HTTT</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr"/>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Biên bản bàn giao</t>
+          <t>Tài liệu, danh sách tham dự</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr"/>
@@ -12186,53 +12260,49 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>4.13.2.2 d)</t>
+          <t>4.13.2.2 b)</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Quy trình vô hiệu hóa mọi quyền ra vào, truy cập, quản trị khi thôi việc</t>
+          <t>Đào tạo nhận thức ≥ 1 lần/năm</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr"/>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Quy trình offboarding, log vô hiệu</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Danh sách, bài kiểm tra</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr"/>
       <c r="H117" s="11" t="inlineStr"/>
       <c r="I117" s="11" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
+          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>4.14.1</t>
+          <t>4.13.2.2 c)</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
         <is>
-          <t>Quy trình đánh giá nhà cung cấp dịch vụ ANM, lưu trữ/xử lý dữ liệu nhạy cảm, nền tảng quan trọng</t>
+          <t>Thu hồi thẻ, dữ liệu, thiết bị, tài sản khi nghỉ hoặc chuyển việc</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr"/>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Quy trình đánh giá NCC</t>
+          <t>Biên bản bàn giao</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr"/>
@@ -12242,31 +12312,35 @@
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
+          <t>Nhân sự vận hành, quản trị, bảo vệ an ninh mạng</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>4.14.2</t>
+          <t>4.13.2.2 d)</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Danh sách nhà cung cấp, theo dõi trạng thái</t>
+          <t>Quy trình vô hiệu hóa mọi quyền ra vào, truy cập, quản trị khi thôi việc</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr"/>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Danh sách NCC</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="inlineStr"/>
+          <t>Quy trình offboarding, log vô hiệu</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H119" s="11" t="inlineStr"/>
       <c r="I119" s="11" t="inlineStr"/>
     </row>
@@ -12283,18 +12357,18 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>4.14.2</t>
+          <t>4.14.1</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
         <is>
-          <t>Phân loại nhà cung cấp</t>
+          <t>Quy trình đánh giá nhà cung cấp dịch vụ ANM, lưu trữ/xử lý dữ liệu nhạy cảm, nền tảng quan trọng</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr"/>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Tiêu chí phân loại</t>
+          <t>Quy trình đánh giá NCC</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr"/>
@@ -12319,13 +12393,13 @@
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Văn bản phân định phạm vi trách nhiệm giữa nhà cung cấp và tổ chức</t>
+          <t>Danh sách nhà cung cấp, theo dõi trạng thái</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr"/>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Hợp đồng/SLA/ma trận RACI</t>
+          <t>Danh sách NCC</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr"/>
@@ -12350,13 +12424,13 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật danh sách nhà cung cấp ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Phân loại nhà cung cấp</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr"/>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Ngày cập nhật</t>
+          <t>Tiêu chí phân loại</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr"/>
@@ -12366,63 +12440,59 @@
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>4.15.1</t>
+          <t>4.14.2</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Chính sách/quy trình sự cố gồm: phân nhóm; tiếp nhận–phân loại–xử lý ban đầu; kế hoạch ứng phó; giám sát cảnh báo; quy trình sự cố thường và nghiêm trọng; cơ chế phối hợp</t>
+          <t>Văn bản phân định phạm vi trách nhiệm giữa nhà cung cấp và tổ chức</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr"/>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Kế hoạch ứng phó sự cố</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Mới/khác so với cấp 1</t>
-        </is>
-      </c>
+          <t>Hợp đồng/SLA/ma trận RACI</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr"/>
       <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+          <t>Quản lý nhà cung cấp sản phẩm, dịch vụ</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.1 a)</t>
+          <t>4.14.2</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Chỉ định người chủ chốt và ít nhất một người dự phòng quản lý ứng phó sự cố</t>
+          <t>Cập nhật danh sách nhà cung cấp ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr"/>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Quyết định phân công</t>
+          <t>Ngày cập nhật</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr"/>
@@ -12442,18 +12512,18 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.1 b)</t>
+          <t>4.15.1</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Đầu mối phối hợp với cơ quan quản lý nhà nước về ANM và cơ quan điều hành Liên minh ứng phó sự cố quốc gia</t>
+          <t>Chính sách/quy trình sự cố gồm: phân nhóm; tiếp nhận–phân loại–xử lý ban đầu; kế hoạch ứng phó; giám sát cảnh báo; quy trình sự cố thường và nghiêm trọng; cơ chế phối hợp</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr"/>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Danh bạ đầu mối, văn bản đăng ký</t>
+          <t>Kế hoạch ứng phó sự cố</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -12477,18 +12547,18 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.1 c)</t>
+          <t>4.15.2.1 a)</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
         <is>
-          <t>Đầu mối tiếp nhận báo cáo sự cố; xác minh thông tin liên hệ hằng năm</t>
+          <t>Chỉ định người chủ chốt và ít nhất một người dự phòng quản lý ứng phó sự cố</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr"/>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Danh bạ có ngày xác minh</t>
+          <t>Quyết định phân công</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr"/>
@@ -12508,21 +12578,25 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.1 d)</t>
+          <t>4.15.2.1 b)</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Phân công vai trò, trách nhiệm từng thành viên đội ứng phó</t>
+          <t>Đầu mối phối hợp với cơ quan quản lý nhà nước về ANM và cơ quan điều hành Liên minh ứng phó sự cố quốc gia</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr"/>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Bảng RACI đội ứng phó</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr"/>
+          <t>Danh bạ đầu mối, văn bản đăng ký</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Mới/khác so với cấp 1</t>
+        </is>
+      </c>
       <c r="H127" s="11" t="inlineStr"/>
       <c r="I127" s="11" t="inlineStr"/>
     </row>
@@ -12539,18 +12613,18 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.1 e)</t>
+          <t>4.15.2.1 c)</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
         <is>
-          <t>Quy định trách nhiệm phối hợp của các phòng ban với đội ứng phó</t>
+          <t>Đầu mối tiếp nhận báo cáo sự cố; xác minh thông tin liên hệ hằng năm</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr"/>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Quy chế phối hợp</t>
+          <t>Danh bạ có ngày xác minh</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr"/>
@@ -12570,18 +12644,18 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.2 a)</t>
+          <t>4.15.2.1 d)</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Quy trình báo cáo sự cố nội bộ</t>
+          <t>Phân công vai trò, trách nhiệm từng thành viên đội ứng phó</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr"/>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Quy trình, mẫu báo cáo</t>
+          <t>Bảng RACI đội ứng phó</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr"/>
@@ -12601,18 +12675,18 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.2 b)</t>
+          <t>4.15.2.1 e)</t>
         </is>
       </c>
       <c r="D130" s="7" t="inlineStr">
         <is>
-          <t>Phân nhóm sự cố ANM</t>
+          <t>Quy định trách nhiệm phối hợp của các phòng ban với đội ứng phó</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr"/>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Bảng phân loại sự cố</t>
+          <t>Quy chế phối hợp</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr"/>
@@ -12632,18 +12706,18 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.2 c)</t>
+          <t>4.15.2.2 a)</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật quy trình báo cáo ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Quy trình báo cáo sự cố nội bộ</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr"/>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Lịch sử phiên bản</t>
+          <t>Quy trình, mẫu báo cáo</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr"/>
@@ -12663,18 +12737,18 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.3 a)</t>
+          <t>4.15.2.2 b)</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Quy trình ứng phó có cơ chế phối hợp với cơ quan chức năng, chuyên gia, nhà cung cấp dịch vụ</t>
+          <t>Phân nhóm sự cố ANM</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr"/>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>Quy trình ứng phó</t>
+          <t>Bảng phân loại sự cố</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr"/>
@@ -12694,12 +12768,12 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>4.15.2.3 b)</t>
+          <t>4.15.2.2 c)</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Cập nhật quy trình ứng phó ≥ 1 lần/năm hoặc khi thay đổi</t>
+          <t>Cập nhật quy trình báo cáo ≥ 1 lần/năm hoặc khi thay đổi</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr"/>
@@ -12712,9 +12786,71 @@
       <c r="H133" s="11" t="inlineStr"/>
       <c r="I133" s="11" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>4.15.2.3 a)</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Quy trình ứng phó có cơ chế phối hợp với cơ quan chức năng, chuyên gia, nhà cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr"/>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>Quy trình ứng phó</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr"/>
+      <c r="H134" s="11" t="inlineStr"/>
+      <c r="I134" s="11" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>Quản trị ứng phó sự cố an ninh mạng</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>4.15.2.3 b)</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Cập nhật quy trình ứng phó ≥ 1 lần/năm hoặc khi thay đổi</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr"/>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>Lịch sử phiên bản</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr"/>
+      <c r="H135" s="11" t="inlineStr"/>
+      <c r="I135" s="11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I133"/>
-  <conditionalFormatting sqref="E5:E133">
+  <autoFilter ref="A4:I135"/>
+  <conditionalFormatting sqref="E5:E135">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Đạt"</formula>
     </cfRule>
@@ -12729,7 +12865,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: Đạt, Một phần, Chưa hoặc N/A" type="list">
+    <dataValidation sqref="E5:E135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: Đạt, Một phần, Chưa hoặc N/A" type="list">
       <formula1>"Đạt,Một phần,Chưa,N/A"</formula1>
     </dataValidation>
   </dataValidations>
